--- a/data/Basic Functions and Conditional formatting task.xlsx
+++ b/data/Basic Functions and Conditional formatting task.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mushin lG\Assignments\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:10000001_{FD767292-EC7E-4EEA-A767-429E930E4E2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="27">
   <si>
     <t>Yearly Sales Report</t>
   </si>
@@ -108,14 +110,20 @@
   </si>
   <si>
     <t>Sum of Sales by Years</t>
+  </si>
+  <si>
+    <t>year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yearly Summary </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="8" x14ac:knownFonts="1">
     <font>
@@ -201,7 +209,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -465,12 +473,116 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="medium">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </left>
+      <right style="thin">
+        <color theme="9" tint="0.39997558519241921"/>
+      </right>
+      <top style="medium">
+        <color theme="9" tint="0.39997558519241921"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom style="thin">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top style="thin">
+        <color theme="9"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color theme="9"/>
+      </left>
+      <right style="thin">
+        <color theme="9"/>
+      </right>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom style="medium">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color theme="9"/>
+      </right>
+      <top style="medium">
+        <color theme="9"/>
+      </top>
+      <bottom style="medium">
+        <color theme="9"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -496,8 +608,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -510,30 +640,54 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -842,25 +996,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:U26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.453125" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="32.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="25" x14ac:dyDescent="0.5">
-      <c r="A1" s="27" t="s">
+    <row r="1" spans="1:21" ht="26.25" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-    </row>
-    <row r="2" spans="1:21" ht="18" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="B1" s="33"/>
+      <c r="C1" s="33"/>
+      <c r="D1" s="33"/>
+      <c r="E1" s="33"/>
+      <c r="F1" s="33"/>
+    </row>
+    <row r="2" spans="1:21" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
@@ -879,8 +1044,11 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="U2" s="37" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -901,11 +1069,11 @@
         <v>16720</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="I3" s="34" t="s">
+      <c r="I3" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="J3" s="35"/>
-      <c r="K3" s="36"/>
+      <c r="J3" s="28"/>
+      <c r="K3" s="29"/>
       <c r="N3" s="7"/>
       <c r="O3" s="8" t="s">
         <v>9</v>
@@ -913,8 +1081,14 @@
       <c r="P3" s="9" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="T3" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="U3" s="39" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>2</v>
       </c>
@@ -947,15 +1121,25 @@
       <c r="K4" s="23">
         <v>2012</v>
       </c>
-      <c r="N4" s="31" t="s">
+      <c r="N4" s="30" t="s">
         <v>12</v>
       </c>
       <c r="O4" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="P4" s="14"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P4" s="14">
+        <f>COUNTIF(D3:D26,D5)</f>
+        <v>6</v>
+      </c>
+      <c r="T4" s="40">
+        <v>2010</v>
+      </c>
+      <c r="U4" s="44">
+        <f>SUM(F3:F11)</f>
+        <v>104720</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>3</v>
       </c>
@@ -978,16 +1162,35 @@
       <c r="H5" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="I5" s="25"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="25"/>
-      <c r="N5" s="32"/>
+      <c r="I5" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H5,C3:C26,I4)</f>
+        <v>12320</v>
+      </c>
+      <c r="J5" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H5,C3:C26,J4)</f>
+        <v>23100</v>
+      </c>
+      <c r="K5" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H5,C3:C26,K4)</f>
+        <v>25520</v>
+      </c>
+      <c r="N5" s="31"/>
       <c r="O5" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="P5" s="14"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P5" s="14">
+        <f>COUNTIF(D3:D26,O5)</f>
+        <v>3</v>
+      </c>
+      <c r="T5" s="41">
+        <v>2011</v>
+      </c>
+      <c r="U5" s="45">
+        <f>SUM(F12:F17)</f>
+        <v>83600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>4</v>
       </c>
@@ -1010,16 +1213,35 @@
       <c r="H6" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="I6" s="25"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="25"/>
-      <c r="N6" s="32"/>
+      <c r="I6" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H6,C3:C26,I4)</f>
+        <v>16720</v>
+      </c>
+      <c r="J6" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H6,C3:C26,J4)</f>
+        <v>6160</v>
+      </c>
+      <c r="K6" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H6,C3:C26,K4)</f>
+        <v>7920</v>
+      </c>
+      <c r="N6" s="31"/>
       <c r="O6" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="14"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="P6" s="14">
+        <f>COUNTIF(D3:D26,O6)</f>
+        <v>5</v>
+      </c>
+      <c r="T6" s="43">
+        <v>2012</v>
+      </c>
+      <c r="U6" s="46">
+        <f>SUM(F18:F26)</f>
+        <v>80960</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <v>5</v>
       </c>
@@ -1042,16 +1264,30 @@
       <c r="H7" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="I7" s="25"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="25"/>
-      <c r="N7" s="32"/>
+      <c r="I7" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H7,C3:C26,I4)</f>
+        <v>26840</v>
+      </c>
+      <c r="J7" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H7,C3:C26,J4)</f>
+        <v>0</v>
+      </c>
+      <c r="K7" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H7,C3:C26,K4)</f>
+        <v>15840</v>
+      </c>
+      <c r="N7" s="31"/>
       <c r="O7" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="P7" s="14"/>
-    </row>
-    <row r="8" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P7" s="14">
+        <f>COUNTIF(D3:D26,O7)</f>
+        <v>3</v>
+      </c>
+      <c r="T7" s="42"/>
+      <c r="U7" s="42"/>
+    </row>
+    <row r="8" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>6</v>
       </c>
@@ -1074,16 +1310,28 @@
       <c r="H8" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="25"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="25"/>
-      <c r="N8" s="33"/>
+      <c r="I8" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H8,C3:C26,I4)</f>
+        <v>19800</v>
+      </c>
+      <c r="J8" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H8,C3:C26,J4)</f>
+        <v>20900</v>
+      </c>
+      <c r="K8" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H8,C3:C26,K4)</f>
+        <v>11440</v>
+      </c>
+      <c r="N8" s="32"/>
       <c r="O8" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="P8" s="14"/>
-    </row>
-    <row r="9" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="P8" s="14">
+        <f>COUNTIF(D3:D26,O8)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>7</v>
       </c>
@@ -1106,11 +1354,20 @@
       <c r="H9" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="25"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="I9" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H9,C3:C26,I4)</f>
+        <v>29040</v>
+      </c>
+      <c r="J9" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H9,C3:C26,J4)</f>
+        <v>33440</v>
+      </c>
+      <c r="K9" s="25">
+        <f>SUMIFS(F3:F26,D3:D26,H9,C3:C26,K4)</f>
+        <v>20240</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <v>8</v>
       </c>
@@ -1131,7 +1388,7 @@
         <v>11000</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <v>9</v>
       </c>
@@ -1152,7 +1409,7 @@
         <v>7260</v>
       </c>
     </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>10</v>
       </c>
@@ -1173,7 +1430,7 @@
         <v>20900</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>11</v>
       </c>
@@ -1194,7 +1451,7 @@
         <v>12540</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>12</v>
       </c>
@@ -1214,13 +1471,13 @@
       <c r="F14" s="4">
         <v>10560</v>
       </c>
-      <c r="H14" s="28" t="s">
+      <c r="H14" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="29"/>
-      <c r="J14" s="30"/>
-    </row>
-    <row r="15" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="I14" s="35"/>
+      <c r="J14" s="36"/>
+    </row>
+    <row r="15" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>13</v>
       </c>
@@ -1257,13 +1514,13 @@
       <c r="O15" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="S15" s="34" t="s">
+      <c r="S15" s="27" t="s">
         <v>22</v>
       </c>
-      <c r="T15" s="35"/>
-      <c r="U15" s="36"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="T15" s="28"/>
+      <c r="U15" s="29"/>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <v>14</v>
       </c>
@@ -1286,16 +1543,28 @@
       <c r="H16" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="I16" s="13"/>
-      <c r="J16" s="16"/>
-      <c r="L16" s="31" t="s">
+      <c r="I16" s="13">
+        <f>SUM(E3:E26)</f>
+        <v>1224</v>
+      </c>
+      <c r="J16" s="16">
+        <f>SUM(F3:F26)</f>
+        <v>269280</v>
+      </c>
+      <c r="L16" s="30" t="s">
         <v>23</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="N16" s="13"/>
-      <c r="O16" s="13"/>
+      <c r="N16" s="13">
+        <f>SUMIF(D3:D26,"Abdul",E3:E26)</f>
+        <v>277</v>
+      </c>
+      <c r="O16" s="13">
+        <f>SUMIF(D3:D26,M16,F3:F26)</f>
+        <v>60940</v>
+      </c>
       <c r="R16" s="20" t="s">
         <v>4</v>
       </c>
@@ -1309,7 +1578,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <v>15</v>
       </c>
@@ -1332,22 +1601,43 @@
       <c r="H17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="I17" s="13"/>
-      <c r="J17" s="16"/>
-      <c r="L17" s="32"/>
+      <c r="I17" s="13">
+        <f>MIN(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J17" s="16">
+        <f>MIN(F3:F26)</f>
+        <v>5280</v>
+      </c>
+      <c r="L17" s="31"/>
       <c r="M17" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="N17" s="13"/>
-      <c r="O17" s="13"/>
+      <c r="N17" s="13">
+        <f>SUMIF(D3:D26,D16,E3:E26)</f>
+        <v>140</v>
+      </c>
+      <c r="O17" s="13">
+        <f>SUMIF(D3:D26,M17,F3:F26)</f>
+        <v>30800</v>
+      </c>
       <c r="R17" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="S17" s="25"/>
-      <c r="T17" s="25"/>
-      <c r="U17" s="25"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="S17" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R17,C3:C26,S16)</f>
+        <v>56</v>
+      </c>
+      <c r="T17" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R17,C3:C26,T16)</f>
+        <v>105</v>
+      </c>
+      <c r="U17" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R17,C3:C26,U16)</f>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <v>16</v>
       </c>
@@ -1370,22 +1660,43 @@
       <c r="H18" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="I18" s="13"/>
-      <c r="J18" s="16"/>
-      <c r="L18" s="32"/>
+      <c r="I18" s="13">
+        <f>MAX(E3:E26)</f>
+        <v>95</v>
+      </c>
+      <c r="J18" s="16">
+        <f>MAX(F3:F26)</f>
+        <v>20900</v>
+      </c>
+      <c r="L18" s="31"/>
       <c r="M18" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="N18" s="13"/>
-      <c r="O18" s="13"/>
+      <c r="N18" s="13">
+        <f>SUMIF(D3:D26,D9,E3:E26)</f>
+        <v>194</v>
+      </c>
+      <c r="O18" s="13">
+        <f>SUMIF(D3:D26,M18,F3:F26)</f>
+        <v>42680</v>
+      </c>
       <c r="R18" s="24" t="s">
         <v>7</v>
       </c>
-      <c r="S18" s="25"/>
-      <c r="T18" s="25"/>
-      <c r="U18" s="25"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="S18" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R18,C3:C26,S16)</f>
+        <v>76</v>
+      </c>
+      <c r="T18" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R18,C3:C26,T16)</f>
+        <v>28</v>
+      </c>
+      <c r="U18" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R18,C3:C26,U16)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <v>17</v>
       </c>
@@ -1408,22 +1719,43 @@
       <c r="H19" s="15" t="s">
         <v>19</v>
       </c>
-      <c r="I19" s="13"/>
-      <c r="J19" s="16"/>
-      <c r="L19" s="32"/>
+      <c r="I19" s="13">
+        <f>AVERAGE(E3:E26)</f>
+        <v>51</v>
+      </c>
+      <c r="J19" s="16">
+        <f>AVERAGE(F3:F26)</f>
+        <v>11220</v>
+      </c>
+      <c r="L19" s="31"/>
       <c r="M19" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
+      <c r="N19" s="13">
+        <f>SUMIF(D3:D26,D12,E3:E26)</f>
+        <v>237</v>
+      </c>
+      <c r="O19" s="13">
+        <f>SUMIF(D3:D26,M19,F3:F26)</f>
+        <v>52140</v>
+      </c>
       <c r="R19" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="S19" s="25"/>
-      <c r="T19" s="25"/>
-      <c r="U19" s="25"/>
-    </row>
-    <row r="20" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S19" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R19,C3:C26,S16)</f>
+        <v>122</v>
+      </c>
+      <c r="T19" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R19,C3:C26,T16)</f>
+        <v>0</v>
+      </c>
+      <c r="U19" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R19,C3:C26,U16)</f>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>18</v>
       </c>
@@ -1446,22 +1778,43 @@
       <c r="H20" s="15" t="s">
         <v>20</v>
       </c>
-      <c r="I20" s="13"/>
-      <c r="J20" s="14"/>
-      <c r="L20" s="33"/>
+      <c r="I20" s="13">
+        <f>COUNT(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J20" s="14">
+        <f>COUNT(F3:F26)</f>
+        <v>24</v>
+      </c>
+      <c r="L20" s="32"/>
       <c r="M20" s="17" t="s">
         <v>11</v>
       </c>
-      <c r="N20" s="13"/>
-      <c r="O20" s="13"/>
+      <c r="N20" s="13">
+        <f>SUMIF(D3:D26,M20,E3:E26)</f>
+        <v>376</v>
+      </c>
+      <c r="O20" s="13">
+        <f>SUMIF(D3:D26,M20,F3:F26)</f>
+        <v>82720</v>
+      </c>
       <c r="R20" s="24" t="s">
         <v>18</v>
       </c>
-      <c r="S20" s="25"/>
-      <c r="T20" s="25"/>
-      <c r="U20" s="25"/>
-    </row>
-    <row r="21" spans="1:21" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="S20" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R20,C3:C26,S16)</f>
+        <v>90</v>
+      </c>
+      <c r="T20" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R20,C3:C26,T16)</f>
+        <v>95</v>
+      </c>
+      <c r="U20" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R20,C3:C26,U16)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>19</v>
       </c>
@@ -1484,16 +1837,31 @@
       <c r="H21" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="I21" s="13"/>
-      <c r="J21" s="19"/>
+      <c r="I21" s="13">
+        <f>COUNTA(E3:E26)</f>
+        <v>24</v>
+      </c>
+      <c r="J21" s="19">
+        <f>COUNTA(F3:F26)</f>
+        <v>24</v>
+      </c>
       <c r="R21" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="S21" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R21,C3:C26,S16)</f>
+        <v>132</v>
+      </c>
+      <c r="T21" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R21,C3:C26,T16)</f>
+        <v>152</v>
+      </c>
+      <c r="U21" s="25">
+        <f>SUMIFS(E3:E26,D3:D26,R21,C3:C26,U16)</f>
+        <v>92</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <v>20</v>
       </c>
@@ -1514,7 +1882,7 @@
         <v>10340</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <v>21</v>
       </c>
@@ -1535,7 +1903,7 @@
         <v>9020</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <v>22</v>
       </c>
@@ -1556,7 +1924,7 @@
         <v>11440</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <v>23</v>
       </c>
@@ -1577,7 +1945,7 @@
         <v>7920</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <v>24</v>
       </c>
@@ -1600,13 +1968,21 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="S15:U15"/>
+    <mergeCell ref="L16:L20"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="H14:J14"/>
     <mergeCell ref="N4:N8"/>
-    <mergeCell ref="S15:U15"/>
-    <mergeCell ref="L16:L20"/>
   </mergeCells>
+  <conditionalFormatting sqref="F3:F26">
+    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+      <formula>15000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+      <formula>6000</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>